--- a/00 DOCS/Copy of HTMLCSSJS + React -TOC.xlsx
+++ b/00 DOCS/Copy of HTMLCSSJS + React -TOC.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2053243_cognizant_com/Documents/Attendance/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ongoing\ReactJS\00 DOCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{545C3E0C-852D-45E2-8842-F53C5A2B40BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4A35AC-D0CE-4045-AD9E-24243E50880D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{DEADF150-DC9C-4EA7-845E-B4B5BA8E0F30}"/>
+    <workbookView xWindow="343" yWindow="2280" windowWidth="20588" windowHeight="15394" activeTab="1" xr2:uid="{DEADF150-DC9C-4EA7-845E-B4B5BA8E0F30}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Eval" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="161">
   <si>
     <t>Date</t>
   </si>
@@ -504,6 +505,21 @@
   </si>
   <si>
     <t>Use case - Evaluation with mentor</t>
+  </si>
+  <si>
+    <t>Jerin</t>
+  </si>
+  <si>
+    <t>Ajeet</t>
+  </si>
+  <si>
+    <t>santhosh</t>
+  </si>
+  <si>
+    <t>Vinay</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -696,15 +712,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -737,6 +744,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1073,836 +1089,836 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F8A68FD-B7FB-4374-BE20-8329B3A8749C}">
   <dimension ref="A1:B141"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="61.26953125" customWidth="1"/>
+    <col min="2" max="2" width="61.23046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:2" ht="17.600000000000001" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="11"/>
-    </row>
-    <row r="3" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="7"/>
-      <c r="B3" s="12" t="s">
+      <c r="B2" s="8"/>
+    </row>
+    <row r="3" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A3" s="18"/>
+      <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="7"/>
-      <c r="B4" s="12" t="s">
+    <row r="4" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A4" s="18"/>
+      <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="7"/>
-      <c r="B5" s="12" t="s">
+    <row r="5" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A5" s="18"/>
+      <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="7"/>
-      <c r="B6" s="12" t="s">
+    <row r="6" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A6" s="18"/>
+      <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="7"/>
-      <c r="B7" s="12" t="s">
+    <row r="7" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A7" s="18"/>
+      <c r="B7" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="7"/>
-      <c r="B8" s="12" t="s">
+    <row r="8" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A8" s="18"/>
+      <c r="B8" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="8"/>
-      <c r="B9" s="13" t="s">
+    <row r="9" spans="1:2" ht="17.600000000000001" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="19"/>
+      <c r="B9" s="10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A10" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="7"/>
-      <c r="B11" s="12" t="s">
+    <row r="11" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A11" s="18"/>
+      <c r="B11" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="7"/>
-      <c r="B12" s="12" t="s">
+    <row r="12" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A12" s="18"/>
+      <c r="B12" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="7"/>
-      <c r="B13" s="12" t="s">
+    <row r="13" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A13" s="18"/>
+      <c r="B13" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="7"/>
-      <c r="B14" s="12" t="s">
+    <row r="14" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A14" s="18"/>
+      <c r="B14" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="7"/>
-      <c r="B15" s="12" t="s">
+    <row r="15" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A15" s="18"/>
+      <c r="B15" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="7"/>
-      <c r="B16" s="12" t="s">
+    <row r="16" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A16" s="18"/>
+      <c r="B16" s="9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="7"/>
-      <c r="B17" s="12" t="s">
+    <row r="17" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A17" s="18"/>
+      <c r="B17" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="8"/>
-      <c r="B18" s="13" t="s">
+    <row r="18" spans="1:2" ht="17.600000000000001" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="19"/>
+      <c r="B18" s="10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="8"/>
-      <c r="B20" s="16" t="s">
+    <row r="20" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="19"/>
+      <c r="B20" s="13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A21" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="7"/>
-      <c r="B22" s="12" t="s">
+    <row r="22" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A22" s="18"/>
+      <c r="B22" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="7"/>
-      <c r="B23" s="12" t="s">
+    <row r="23" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A23" s="18"/>
+      <c r="B23" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="7"/>
-      <c r="B24" s="12" t="s">
+    <row r="24" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A24" s="18"/>
+      <c r="B24" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="7"/>
-      <c r="B25" s="12" t="s">
+    <row r="25" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A25" s="18"/>
+      <c r="B25" s="9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="7"/>
-      <c r="B26" s="12" t="s">
+    <row r="26" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A26" s="18"/>
+      <c r="B26" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="33" x14ac:dyDescent="0.35">
-      <c r="A27" s="7"/>
-      <c r="B27" s="12" t="s">
+    <row r="27" spans="1:2" ht="34.299999999999997" x14ac:dyDescent="0.4">
+      <c r="A27" s="18"/>
+      <c r="B27" s="9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="7"/>
-      <c r="B28" s="12" t="s">
+    <row r="28" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A28" s="18"/>
+      <c r="B28" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="7"/>
-      <c r="B29" s="12" t="s">
+    <row r="29" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A29" s="18"/>
+      <c r="B29" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="7"/>
-      <c r="B30" s="12" t="s">
+    <row r="30" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A30" s="18"/>
+      <c r="B30" s="9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="7"/>
-      <c r="B31" s="12" t="s">
+    <row r="31" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A31" s="18"/>
+      <c r="B31" s="9" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="7"/>
-      <c r="B32" s="12" t="s">
+    <row r="32" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A32" s="18"/>
+      <c r="B32" s="9" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="7"/>
-      <c r="B33" s="12" t="s">
+    <row r="33" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A33" s="18"/>
+      <c r="B33" s="9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="8"/>
-      <c r="B34" s="13" t="s">
+    <row r="34" spans="1:2" ht="17.600000000000001" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="19"/>
+      <c r="B34" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="6" t="s">
+    <row r="35" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="12" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="7"/>
-      <c r="B36" s="15" t="s">
+    <row r="36" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="18"/>
+      <c r="B36" s="12" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="8"/>
-      <c r="B37" s="16" t="s">
+    <row r="37" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="19"/>
+      <c r="B37" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="6" t="s">
+    <row r="38" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A38" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="9" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="7"/>
-      <c r="B39" s="12" t="s">
+    <row r="39" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A39" s="18"/>
+      <c r="B39" s="9" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="7"/>
-      <c r="B40" s="12" t="s">
+    <row r="40" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A40" s="18"/>
+      <c r="B40" s="9" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="7"/>
-      <c r="B41" s="12" t="s">
+    <row r="41" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A41" s="18"/>
+      <c r="B41" s="9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="7"/>
-      <c r="B42" s="12" t="s">
+    <row r="42" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A42" s="18"/>
+      <c r="B42" s="9" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="8"/>
-      <c r="B43" s="13" t="s">
+    <row r="43" spans="1:2" ht="17.600000000000001" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="19"/>
+      <c r="B43" s="10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="6" t="s">
+    <row r="44" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="12" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="8"/>
-      <c r="B45" s="16" t="s">
+    <row r="45" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="19"/>
+      <c r="B45" s="13" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A46" s="6" t="s">
+    <row r="46" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A46" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="9" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A47" s="7"/>
-      <c r="B47" s="12" t="s">
+    <row r="47" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A47" s="18"/>
+      <c r="B47" s="9" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="7"/>
-      <c r="B48" s="12" t="s">
+    <row r="48" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A48" s="18"/>
+      <c r="B48" s="9" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="7"/>
-      <c r="B49" s="12" t="s">
+    <row r="49" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A49" s="18"/>
+      <c r="B49" s="9" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A50" s="7"/>
-      <c r="B50" s="12" t="s">
+    <row r="50" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A50" s="18"/>
+      <c r="B50" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A51" s="7"/>
-      <c r="B51" s="12" t="s">
+    <row r="51" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A51" s="18"/>
+      <c r="B51" s="9" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="7"/>
-      <c r="B52" s="12" t="s">
+    <row r="52" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A52" s="18"/>
+      <c r="B52" s="9" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="8"/>
-      <c r="B53" s="13" t="s">
+    <row r="53" spans="1:2" ht="17.600000000000001" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A53" s="19"/>
+      <c r="B53" s="10" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="6" t="s">
+    <row r="54" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="12" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="8"/>
-      <c r="B55" s="16" t="s">
+    <row r="55" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="19"/>
+      <c r="B55" s="13" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="6" t="s">
+    <row r="56" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A56" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A57" s="7"/>
-      <c r="B57" s="12" t="s">
+    <row r="57" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A57" s="18"/>
+      <c r="B57" s="9" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A58" s="7"/>
-      <c r="B58" s="12" t="s">
+    <row r="58" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A58" s="18"/>
+      <c r="B58" s="9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A59" s="7"/>
-      <c r="B59" s="12" t="s">
+    <row r="59" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A59" s="18"/>
+      <c r="B59" s="9" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A60" s="7"/>
-      <c r="B60" s="12" t="s">
+    <row r="60" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A60" s="18"/>
+      <c r="B60" s="9" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A61" s="7"/>
-      <c r="B61" s="12" t="s">
+    <row r="61" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A61" s="18"/>
+      <c r="B61" s="9" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A62" s="7"/>
-      <c r="B62" s="12" t="s">
+    <row r="62" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A62" s="18"/>
+      <c r="B62" s="9" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="8"/>
-      <c r="B63" s="13" t="s">
+    <row r="63" spans="1:2" ht="17.600000000000001" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="19"/>
+      <c r="B63" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="6" t="s">
+    <row r="64" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B64" s="15" t="s">
+      <c r="B64" s="12" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="8"/>
-      <c r="B65" s="16" t="s">
+    <row r="65" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A65" s="19"/>
+      <c r="B65" s="13" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="33" x14ac:dyDescent="0.35">
-      <c r="A66" s="6" t="s">
+    <row r="66" spans="1:2" ht="34.299999999999997" x14ac:dyDescent="0.4">
+      <c r="A66" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B66" s="12" t="s">
+      <c r="B66" s="9" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A67" s="7"/>
-      <c r="B67" s="12" t="s">
+    <row r="67" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A67" s="18"/>
+      <c r="B67" s="9" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A68" s="7"/>
-      <c r="B68" s="12" t="s">
+    <row r="68" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A68" s="18"/>
+      <c r="B68" s="9" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A69" s="7"/>
-      <c r="B69" s="12" t="s">
+    <row r="69" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A69" s="18"/>
+      <c r="B69" s="9" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A70" s="7"/>
-      <c r="B70" s="12" t="s">
+    <row r="70" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A70" s="18"/>
+      <c r="B70" s="9" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A71" s="7"/>
-      <c r="B71" s="12" t="s">
+    <row r="71" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A71" s="18"/>
+      <c r="B71" s="9" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A72" s="7"/>
-      <c r="B72" s="12" t="s">
+    <row r="72" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A72" s="18"/>
+      <c r="B72" s="9" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="8"/>
-      <c r="B73" s="13" t="s">
+    <row r="73" spans="1:2" ht="17.600000000000001" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A73" s="19"/>
+      <c r="B73" s="10" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="6" t="s">
+    <row r="74" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="12" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="8"/>
-      <c r="B75" s="16" t="s">
+    <row r="75" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A75" s="19"/>
+      <c r="B75" s="13" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A76" s="6" t="s">
+    <row r="76" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A76" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B76" s="12" t="s">
+      <c r="B76" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A77" s="7"/>
-      <c r="B77" s="12" t="s">
+    <row r="77" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A77" s="18"/>
+      <c r="B77" s="9" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A78" s="7"/>
-      <c r="B78" s="12" t="s">
+    <row r="78" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A78" s="18"/>
+      <c r="B78" s="9" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A79" s="7"/>
-      <c r="B79" s="12" t="s">
+    <row r="79" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A79" s="18"/>
+      <c r="B79" s="9" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A80" s="7"/>
-      <c r="B80" s="12" t="s">
+    <row r="80" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A80" s="18"/>
+      <c r="B80" s="9" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A81" s="7"/>
-      <c r="B81" s="12" t="s">
+    <row r="81" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A81" s="18"/>
+      <c r="B81" s="9" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A82" s="7"/>
-      <c r="B82" s="12" t="s">
+    <row r="82" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A82" s="18"/>
+      <c r="B82" s="9" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="8"/>
-      <c r="B83" s="13" t="s">
+    <row r="83" spans="1:2" ht="34.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A83" s="19"/>
+      <c r="B83" s="10" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="6" t="s">
+    <row r="84" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B84" s="15" t="s">
+      <c r="B84" s="12" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="8"/>
-      <c r="B85" s="16" t="s">
+    <row r="85" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A85" s="19"/>
+      <c r="B85" s="13" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A86" s="6" t="s">
+    <row r="86" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A86" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B86" s="12" t="s">
+      <c r="B86" s="9" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A87" s="7"/>
-      <c r="B87" s="12" t="s">
+    <row r="87" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A87" s="18"/>
+      <c r="B87" s="9" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A88" s="7"/>
-      <c r="B88" s="12" t="s">
+    <row r="88" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A88" s="18"/>
+      <c r="B88" s="9" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A89" s="7"/>
-      <c r="B89" s="12" t="s">
+    <row r="89" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A89" s="18"/>
+      <c r="B89" s="9" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A90" s="7"/>
-      <c r="B90" s="12" t="s">
+    <row r="90" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A90" s="18"/>
+      <c r="B90" s="9" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A91" s="7"/>
-      <c r="B91" s="12" t="s">
+    <row r="91" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A91" s="18"/>
+      <c r="B91" s="9" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A92" s="7"/>
-      <c r="B92" s="12" t="s">
+    <row r="92" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A92" s="18"/>
+      <c r="B92" s="9" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A93" s="7"/>
-      <c r="B93" s="12" t="s">
+    <row r="93" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A93" s="18"/>
+      <c r="B93" s="9" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A94" s="7"/>
-      <c r="B94" s="12" t="s">
+    <row r="94" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A94" s="18"/>
+      <c r="B94" s="9" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="8"/>
-      <c r="B95" s="13" t="s">
+    <row r="95" spans="1:2" ht="17.600000000000001" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A95" s="19"/>
+      <c r="B95" s="10" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="6" t="s">
+    <row r="96" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A96" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B96" s="15" t="s">
+      <c r="B96" s="12" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="8"/>
-      <c r="B97" s="16" t="s">
+    <row r="97" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A97" s="19"/>
+      <c r="B97" s="13" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A98" s="6" t="s">
+    <row r="98" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A98" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="B98" s="12" t="s">
+      <c r="B98" s="9" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A99" s="7"/>
-      <c r="B99" s="12" t="s">
+    <row r="99" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A99" s="18"/>
+      <c r="B99" s="9" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A100" s="7"/>
-      <c r="B100" s="12" t="s">
+    <row r="100" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A100" s="18"/>
+      <c r="B100" s="9" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A101" s="7"/>
-      <c r="B101" s="12" t="s">
+    <row r="101" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A101" s="18"/>
+      <c r="B101" s="9" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A102" s="7"/>
-      <c r="B102" s="12" t="s">
+    <row r="102" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A102" s="18"/>
+      <c r="B102" s="9" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="8"/>
-      <c r="B103" s="13" t="s">
+    <row r="103" spans="1:2" ht="17.600000000000001" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A103" s="19"/>
+      <c r="B103" s="10" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="6" t="s">
+    <row r="104" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A104" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="B104" s="15" t="s">
+      <c r="B104" s="12" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="8"/>
-      <c r="B105" s="16" t="s">
+    <row r="105" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A105" s="19"/>
+      <c r="B105" s="13" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A106" s="6" t="s">
+    <row r="106" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A106" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="B106" s="12" t="s">
+      <c r="B106" s="9" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A107" s="7"/>
-      <c r="B107" s="12" t="s">
+    <row r="107" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A107" s="18"/>
+      <c r="B107" s="9" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A108" s="7"/>
-      <c r="B108" s="12" t="s">
+    <row r="108" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A108" s="18"/>
+      <c r="B108" s="9" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A109" s="7"/>
-      <c r="B109" s="12" t="s">
+    <row r="109" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A109" s="18"/>
+      <c r="B109" s="9" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A110" s="7"/>
-      <c r="B110" s="12" t="s">
+    <row r="110" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A110" s="18"/>
+      <c r="B110" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A111" s="7"/>
-      <c r="B111" s="12" t="s">
+    <row r="111" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A111" s="18"/>
+      <c r="B111" s="9" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A112" s="8"/>
-      <c r="B112" s="13" t="s">
+    <row r="112" spans="1:2" ht="17.600000000000001" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A112" s="19"/>
+      <c r="B112" s="10" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="6" t="s">
+    <row r="113" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A113" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="B113" s="15" t="s">
+      <c r="B113" s="12" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="8"/>
-      <c r="B114" s="16" t="s">
+    <row r="114" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A114" s="19"/>
+      <c r="B114" s="13" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A115" s="6" t="s">
+    <row r="115" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A115" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="B115" s="12" t="s">
+      <c r="B115" s="9" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A116" s="7"/>
-      <c r="B116" s="12" t="s">
+    <row r="116" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A116" s="18"/>
+      <c r="B116" s="9" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A117" s="7"/>
-      <c r="B117" s="12" t="s">
+    <row r="117" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A117" s="18"/>
+      <c r="B117" s="9" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A118" s="7"/>
-      <c r="B118" s="12" t="s">
+    <row r="118" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A118" s="18"/>
+      <c r="B118" s="9" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A119" s="7"/>
-      <c r="B119" s="12" t="s">
+    <row r="119" spans="1:2" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A119" s="18"/>
+      <c r="B119" s="9" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="8"/>
-      <c r="B120" s="13" t="s">
+    <row r="120" spans="1:2" ht="17.600000000000001" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A120" s="19"/>
+      <c r="B120" s="10" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="6" t="s">
+    <row r="121" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A121" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="B121" s="14" t="s">
+      <c r="B121" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="8"/>
-      <c r="B122" s="14" t="s">
+    <row r="122" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A122" s="19"/>
+      <c r="B122" s="11" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="6" t="s">
+    <row r="123" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A123" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="B123" s="17" t="s">
+      <c r="B123" s="14" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="124" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="7"/>
-      <c r="B124" s="15" t="s">
+    <row r="124" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A124" s="18"/>
+      <c r="B124" s="12" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="125" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A125" s="7"/>
-      <c r="B125" s="15" t="s">
+    <row r="125" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A125" s="18"/>
+      <c r="B125" s="12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="126" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="7"/>
-      <c r="B126" s="15" t="s">
+    <row r="126" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A126" s="18"/>
+      <c r="B126" s="12" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="127" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="7"/>
-      <c r="B127" s="15" t="s">
+    <row r="127" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A127" s="18"/>
+      <c r="B127" s="12" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="8"/>
-      <c r="B128" s="16" t="s">
+    <row r="128" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A128" s="19"/>
+      <c r="B128" s="13" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:2" ht="17.600000000000001" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A129" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B129" s="16" t="s">
+      <c r="B129" s="13" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:2" ht="17.600000000000001" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
         <v>141</v>
       </c>
@@ -1910,7 +1926,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:2" ht="17.600000000000001" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A131" s="1" t="s">
         <v>141</v>
       </c>
@@ -1918,7 +1934,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:2" ht="17.600000000000001" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A132" s="1" t="s">
         <v>141</v>
       </c>
@@ -1926,7 +1942,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:2" ht="17.600000000000001" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A133" s="1" t="s">
         <v>141</v>
       </c>
@@ -1934,57 +1950,57 @@
         <v>145</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:2" ht="17.600000000000001" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B134" s="18" t="s">
+      <c r="B134" s="15" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="135" spans="1:2" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:2" ht="17.600000000000001" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A135" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B135" s="18" t="s">
+      <c r="B135" s="15" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="136" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="6" t="s">
+    <row r="136" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A136" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="B136" s="19" t="s">
+      <c r="B136" s="16" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="137" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A137" s="7"/>
-      <c r="B137" s="19" t="s">
+    <row r="137" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A137" s="18"/>
+      <c r="B137" s="16" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="138" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="7"/>
-      <c r="B138" s="19" t="s">
+    <row r="138" spans="1:2" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A138" s="18"/>
+      <c r="B138" s="16" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="139" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A139" s="8"/>
-      <c r="B139" s="18" t="s">
+    <row r="139" spans="1:2" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A139" s="19"/>
+      <c r="B139" s="15" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="140" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A140" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B140" s="18" t="s">
+      <c r="B140" s="15" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A141" s="5"/>
     </row>
   </sheetData>
@@ -2017,4 +2033,46 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C2000B8-E231-4D61-A6E0-4E47CBAEAFAC}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>